--- a/backtest_runs/20260410_193731/by_symbol/JVDC/JVDC.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/JVDC/JVDC.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>100000</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>100000</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>100000</v>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>100000</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>100000</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>100000</v>
@@ -1185,7 +1185,7 @@
         <v>-6554.019999999993</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>93445.98000000001</v>
@@ -1277,7 +1277,7 @@
         <v>-5621.849999999995</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>87824.13</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>87824.13</v>
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>87824.13</v>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>87824.13</v>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>87824.13</v>
